--- a/output/pdf_financials_xlsx/OPW.xlsx
+++ b/output/pdf_financials_xlsx/OPW.xlsx
@@ -5895,22 +5895,22 @@
         <v>1.838897</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>1.838897</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>3.206458</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>3.377371</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>3.377371</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>3.436296</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>3.589954</v>
       </c>
     </row>
     <row r="93">
@@ -10142,7 +10142,11 @@
           <t>Reserves 8</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
           <t>-</t>
@@ -11866,7 +11870,11 @@
           <t>Reserves 8</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr"/>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E37" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/OPW.xlsx
+++ b/output/pdf_financials_xlsx/OPW.xlsx
@@ -1047,10 +1047,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.001857</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>1.9e-05</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>0</v>
@@ -1083,19 +1083,19 @@
         <v>0</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>0.002269</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>0.010655</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>0.001046</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>0.006767</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>0</v>
+        <v>0.007952000000000001</v>
       </c>
     </row>
     <row r="13">
@@ -1991,10 +1991,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-1.450931</v>
+        <v>-1.452788</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.853131</v>
+        <v>-0.85315</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>-0.501059</v>
@@ -2027,19 +2027,19 @@
         <v>-0.363348</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-2.797409</v>
+        <v>-2.799678</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-2.640849</v>
+        <v>-2.651504</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-2.004589</v>
+        <v>-2.005635</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>-0.436902</v>
+        <v>-0.443669</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>-2.248315</v>
+        <v>-2.256267</v>
       </c>
     </row>
     <row r="28">
@@ -2107,10 +2107,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-1.450931</v>
+        <v>-1.452788</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.853131</v>
+        <v>-0.85315</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>-0.497688</v>
@@ -2143,19 +2143,19 @@
         <v>-0.363087</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-2.796824</v>
+        <v>-2.799093</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-2.639322</v>
+        <v>-2.649977</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-2.003367</v>
+        <v>-2.004413</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-0.431459</v>
+        <v>-0.438226</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>-2.248315</v>
+        <v>-2.256267</v>
       </c>
     </row>
     <row r="30">
@@ -2444,25 +2444,25 @@
         <v>0.005073</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>9.500000000000001e-05</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.164834</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>3.212531</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.271867</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.056365</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.414058</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>0.116427</v>
       </c>
     </row>
     <row r="35">
@@ -2560,25 +2560,25 @@
         <v>0.005073</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>9.500000000000001e-05</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.164834</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>3.212531</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.271867</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.056365</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>0.414058</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>0.116427</v>
       </c>
     </row>
     <row r="37">
@@ -3256,25 +3256,25 @@
         <v>0.127359</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.001829</v>
+        <v>0.001734</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.174967</v>
+        <v>0.010133</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>3.380591</v>
+        <v>0.16806</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>1.105458</v>
+        <v>0.833591</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.800435</v>
+        <v>0.74407</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>1.252578</v>
+        <v>0.83852</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>0.49296</v>
+        <v>0.376533</v>
       </c>
     </row>
     <row r="49">
@@ -8543,7 +8543,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -32504,7 +32504,7 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
@@ -35290,7 +35290,7 @@
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
@@ -37308,7 +37308,7 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
@@ -39696,7 +39696,7 @@
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
@@ -44682,7 +44682,7 @@
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E367" s="5" t="n">

--- a/output/pdf_financials_xlsx/OPW.xlsx
+++ b/output/pdf_financials_xlsx/OPW.xlsx
@@ -1337,10 +1337,10 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>0.51329</v>
+        <v>-0.51329</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>0.06438199999999999</v>
+        <v>-0.06438199999999999</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>-0</v>
@@ -6915,49 +6915,49 @@
         </is>
       </c>
       <c r="B111" s="3" t="n">
-        <v>0</v>
+        <v>-0.000611</v>
       </c>
       <c r="C111" s="3" t="n">
-        <v>0</v>
+        <v>-0.010714</v>
       </c>
       <c r="D111" s="3" t="n">
-        <v>0</v>
+        <v>-0.013615</v>
       </c>
       <c r="E111" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F111" s="3" t="n">
-        <v>0</v>
+        <v>-0.006697</v>
       </c>
       <c r="G111" s="3" t="n">
-        <v>0</v>
+        <v>-0.002069</v>
       </c>
       <c r="H111" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I111" s="3" t="n">
-        <v>0</v>
+        <v>-0.0007649999999999999</v>
       </c>
       <c r="J111" s="3" t="n">
         <v>0</v>
       </c>
       <c r="K111" s="3" t="n">
-        <v>0</v>
+        <v>-0.00026</v>
       </c>
       <c r="L111" s="3" t="n">
-        <v>0</v>
+        <v>-9.6e-05</v>
       </c>
       <c r="M111" s="3" t="n">
         <v>0</v>
       </c>
       <c r="N111" s="3" t="n">
-        <v>0</v>
+        <v>-0.008099</v>
       </c>
       <c r="O111" s="3" t="n">
-        <v>0</v>
+        <v>-0.000408</v>
       </c>
       <c r="P111" s="3" t="n">
-        <v>0</v>
+        <v>-0.000148</v>
       </c>
       <c r="Q111" s="3" t="n">
         <v>0</v>
@@ -7192,7 +7192,7 @@
         <v>0</v>
       </c>
       <c r="Q115" s="3" t="n">
-        <v>0</v>
+        <v>0.06843</v>
       </c>
       <c r="R115" s="3" t="n">
         <v>0</v>
@@ -8287,49 +8287,49 @@
         </is>
       </c>
       <c r="B134" s="3" t="n">
-        <v>0</v>
+        <v>-0.000611</v>
       </c>
       <c r="C134" s="3" t="n">
-        <v>0</v>
+        <v>-0.010714</v>
       </c>
       <c r="D134" s="3" t="n">
-        <v>0</v>
+        <v>-0.013615</v>
       </c>
       <c r="E134" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F134" s="3" t="n">
-        <v>0</v>
+        <v>-0.006697</v>
       </c>
       <c r="G134" s="3" t="n">
-        <v>0</v>
+        <v>-0.002069</v>
       </c>
       <c r="H134" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I134" s="3" t="n">
-        <v>0</v>
+        <v>-0.0007649999999999999</v>
       </c>
       <c r="J134" s="3" t="n">
         <v>0</v>
       </c>
       <c r="K134" s="3" t="n">
-        <v>0</v>
+        <v>-0.00026</v>
       </c>
       <c r="L134" s="3" t="n">
-        <v>0</v>
+        <v>-9.6e-05</v>
       </c>
       <c r="M134" s="3" t="n">
         <v>0</v>
       </c>
       <c r="N134" s="3" t="n">
-        <v>0</v>
+        <v>-0.008099</v>
       </c>
       <c r="O134" s="3" t="n">
-        <v>0</v>
+        <v>-0.000408</v>
       </c>
       <c r="P134" s="3" t="n">
-        <v>0</v>
+        <v>-0.000148</v>
       </c>
       <c r="Q134" s="3" t="n">
         <v>0</v>
@@ -8345,10 +8345,10 @@
         </is>
       </c>
       <c r="B135" s="3" t="n">
-        <v>-0.582915</v>
+        <v>-0.583526</v>
       </c>
       <c r="C135" s="3" t="n">
-        <v>-0.841035</v>
+        <v>-0.851749</v>
       </c>
       <c r="D135" s="1" t="inlineStr">
         <is>
@@ -8359,37 +8359,37 @@
         <v>-0.45086</v>
       </c>
       <c r="F135" s="3" t="n">
-        <v>-1.943164</v>
+        <v>-1.949861</v>
       </c>
       <c r="G135" s="3" t="n">
-        <v>-0.49624</v>
+        <v>-0.498309</v>
       </c>
       <c r="H135" s="3" t="n">
         <v>-0.098508</v>
       </c>
       <c r="I135" s="3" t="n">
-        <v>-0.209217</v>
+        <v>-0.209982</v>
       </c>
       <c r="J135" s="3" t="n">
         <v>-0.377367</v>
       </c>
       <c r="K135" s="3" t="n">
-        <v>-0.456935</v>
+        <v>-0.457195</v>
       </c>
       <c r="L135" s="3" t="n">
-        <v>-0.132428</v>
+        <v>-0.132524</v>
       </c>
       <c r="M135" s="3" t="n">
         <v>-0.352306</v>
       </c>
       <c r="N135" s="3" t="n">
-        <v>-1.478964</v>
+        <v>-1.487063</v>
       </c>
       <c r="O135" s="3" t="n">
-        <v>-2.641885</v>
+        <v>-2.642293</v>
       </c>
       <c r="P135" s="3" t="n">
-        <v>-0.8325669999999999</v>
+        <v>-0.832715</v>
       </c>
       <c r="Q135" s="3" t="n">
         <v>-0.227815</v>
@@ -18097,7 +18097,11 @@
           <t>Proceeds from sale of investments 13</t>
         </is>
       </c>
-      <c r="D100" t="inlineStr"/>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E100" t="inlineStr">
         <is>
           <t>-</t>
@@ -19158,7 +19162,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D111" t="inlineStr"/>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E111" t="inlineStr">
         <is>
           <t>-</t>
@@ -19762,7 +19770,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D117" t="inlineStr"/>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E117" t="inlineStr">
         <is>
           <t>-</t>
@@ -20069,7 +20081,11 @@
           <t>Proceeds from share issuance 8</t>
         </is>
       </c>
-      <c r="D120" t="inlineStr"/>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E120" t="inlineStr">
         <is>
           <t>-</t>
@@ -21419,7 +21435,11 @@
           <t>Proceeds from share issuance</t>
         </is>
       </c>
-      <c r="D134" t="inlineStr"/>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E134" t="inlineStr">
         <is>
           <t>-</t>
@@ -22397,7 +22417,11 @@
           <t>Purchase of equipment 6</t>
         </is>
       </c>
-      <c r="D144" t="inlineStr"/>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E144" t="inlineStr">
         <is>
           <t>-</t>
@@ -25739,7 +25763,11 @@
           <t>Acquisition of equipment</t>
         </is>
       </c>
-      <c r="D178" t="inlineStr"/>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E178" t="inlineStr">
         <is>
           <t>-</t>
@@ -29062,7 +29090,11 @@
           <t>Future income tax recovery</t>
         </is>
       </c>
-      <c r="D211" t="inlineStr"/>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E211" s="5" t="n">
         <v>-0.51329</v>
       </c>
@@ -30173,7 +30205,11 @@
           <t>Acquisition of equipment</t>
         </is>
       </c>
-      <c r="D222" t="inlineStr"/>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E222" s="5" t="n">
         <v>-0.000611</v>
       </c>
@@ -45286,7 +45322,11 @@
           <t>Future income tax recovery</t>
         </is>
       </c>
-      <c r="D373" t="inlineStr"/>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E373" s="5" t="n">
         <v>0.51329</v>
       </c>
